--- a/03_Outputs/Cartama/02_Demografia/demografia.xlsx
+++ b/03_Outputs/Cartama/02_Demografia/demografia.xlsx
@@ -15,6 +15,7 @@
     <sheet name="_fig_03" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="_fig_04" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="_fig_05" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="_mapa02_densidad" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -111,7 +112,7 @@
     <numFmt numFmtId="251" formatCode="0.00"/>
     <numFmt numFmtId="252" formatCode="0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,23 +122,140 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -157,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -180,76 +298,97 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="192" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="198" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="200" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="204" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="206" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="212" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="214" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="216" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="218" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="220" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="222" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="224" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="226" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="228" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="232" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="234" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="234" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="235" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="236" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="236" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="238" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="239" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="241" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="242" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="243" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="244" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="245" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="247" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="248" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="248" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="249" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="250" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="250" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="251" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="14" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -578,19 +717,19 @@
   <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1334,6 +1473,222 @@
       </c>
       <c r="M15" s="21">
         <v>110.316120812453</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="112" t="inlineStr">
+        <is>
+          <t>Código DANE</t>
+        </is>
+      </c>
+      <c r="B1" s="112" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
+      <c r="C1" s="112" t="inlineStr">
+        <is>
+          <t>Población total</t>
+        </is>
+      </c>
+      <c r="D1" s="112" t="inlineStr">
+        <is>
+          <t>Densidad poblacional (hab/km²)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>5145</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Caramanta</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>4499</v>
+      </c>
+      <c r="D2">
+        <v>48.8714794366868</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>5282</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fredonia</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>26401</v>
+      </c>
+      <c r="D3">
+        <v>102.292743388585</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>5368</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jericó</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>14376</v>
+      </c>
+      <c r="D4">
+        <v>70.1265980215597</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>5390</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>La Pintada</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>8654</v>
+      </c>
+      <c r="D5">
+        <v>159.384677165268</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5467</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Montebello</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>6538</v>
+      </c>
+      <c r="D6">
+        <v>85.9941223056863</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>5576</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pueblorrico</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>9053</v>
+      </c>
+      <c r="D7">
+        <v>120.014009809518</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5679</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>29470</v>
+      </c>
+      <c r="D8">
+        <v>150.22703857709</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5789</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Támesis</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>16674</v>
+      </c>
+      <c r="D9">
+        <v>66.1037778408148</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5792</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tarso</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>6556</v>
+      </c>
+      <c r="D10">
+        <v>54.4160943085696</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5856</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>6714</v>
+      </c>
+      <c r="D11">
+        <v>53.2119110543489</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>5861</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Venecia</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>12412</v>
+      </c>
+      <c r="D12">
+        <v>88.8638719604199</v>
       </c>
     </row>
   </sheetData>
@@ -1348,185 +1703,185 @@
   <dimension ref="A1:AG13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="8" max="14" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="17" max="23" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="24" max="24" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="25" max="25" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="26" max="32" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="33" max="33" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="8" max="14" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="17" max="23" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="24" max="24" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="25" max="25" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="26" max="32" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="33" max="33" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>Población masculina</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="23" t="inlineStr">
         <is>
           <t>Población femenina</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>0 a 9</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="23" t="inlineStr">
         <is>
           <t>10 a 19</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="23" t="inlineStr">
         <is>
           <t>20 a 29</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="23" t="inlineStr">
         <is>
           <t>30 a 39</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="23" t="inlineStr">
         <is>
           <t>40 a 49</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="23" t="inlineStr">
         <is>
           <t>50 a 59</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="23" t="inlineStr">
         <is>
           <t>60 a 69</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="23" t="inlineStr">
         <is>
           <t>70 a 79</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="23" t="inlineStr">
         <is>
           <t>80 o más</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="23" t="inlineStr">
         <is>
           <t>Hombres 0 a 9</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="23" t="inlineStr">
         <is>
           <t>Hombres 10 a 19</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="23" t="inlineStr">
         <is>
           <t>Hombres 20 a 29</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="23" t="inlineStr">
         <is>
           <t>Hombres 30 a 39</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="T1" s="23" t="inlineStr">
         <is>
           <t>Hombres 40 a 49</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="U1" s="23" t="inlineStr">
         <is>
           <t>Hombres 50 a 59</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="V1" s="23" t="inlineStr">
         <is>
           <t>Hombres 60 a 69</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="W1" s="23" t="inlineStr">
         <is>
           <t>Hombres 70 a 79</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="X1" s="23" t="inlineStr">
         <is>
           <t>Hombres 80 o más</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Y1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 0 a 9</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="Z1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 10 a 19</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AA1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 20 a 29</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AB1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 30 a 39</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AC1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 40 a 49</t>
         </is>
       </c>
-      <c r="AD1" s="2" t="inlineStr">
+      <c r="AD1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 50 a 59</t>
         </is>
       </c>
-      <c r="AE1" s="2" t="inlineStr">
+      <c r="AE1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 60 a 69</t>
         </is>
       </c>
-      <c r="AF1" s="2" t="inlineStr">
+      <c r="AF1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 70 a 79</t>
         </is>
       </c>
-      <c r="AG1" s="2" t="inlineStr">
+      <c r="AG1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 80 o más</t>
         </is>
@@ -1551,91 +1906,91 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="25">
         <v>2483</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="27">
         <v>2490</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="29">
         <v>546</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="31">
         <v>620</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="33">
         <v>567</v>
       </c>
-      <c r="J2" s="32">
+      <c r="J2" s="35">
         <v>713</v>
       </c>
-      <c r="K2" s="34">
+      <c r="K2" s="37">
         <v>704</v>
       </c>
-      <c r="L2" s="36">
+      <c r="L2" s="39">
         <v>646</v>
       </c>
-      <c r="M2" s="38">
+      <c r="M2" s="41">
         <v>686</v>
       </c>
-      <c r="N2" s="40">
+      <c r="N2" s="43">
         <v>363</v>
       </c>
-      <c r="O2" s="42">
+      <c r="O2" s="45">
         <v>128</v>
       </c>
-      <c r="P2" s="44">
+      <c r="P2" s="47">
         <v>279</v>
       </c>
-      <c r="Q2" s="46">
+      <c r="Q2" s="49">
         <v>324</v>
       </c>
-      <c r="R2" s="48">
+      <c r="R2" s="51">
         <v>280</v>
       </c>
-      <c r="S2" s="50">
+      <c r="S2" s="53">
         <v>354</v>
       </c>
-      <c r="T2" s="52">
+      <c r="T2" s="55">
         <v>358</v>
       </c>
-      <c r="U2" s="54">
+      <c r="U2" s="57">
         <v>309</v>
       </c>
-      <c r="V2" s="56">
+      <c r="V2" s="59">
         <v>347</v>
       </c>
-      <c r="W2" s="58">
+      <c r="W2" s="61">
         <v>173</v>
       </c>
-      <c r="X2" s="60">
+      <c r="X2" s="63">
         <v>59</v>
       </c>
-      <c r="Y2" s="62">
+      <c r="Y2" s="65">
         <v>267</v>
       </c>
-      <c r="Z2" s="64">
+      <c r="Z2" s="67">
         <v>296</v>
       </c>
-      <c r="AA2" s="66">
+      <c r="AA2" s="69">
         <v>287</v>
       </c>
-      <c r="AB2" s="68">
+      <c r="AB2" s="71">
         <v>359</v>
       </c>
-      <c r="AC2" s="70">
+      <c r="AC2" s="73">
         <v>346</v>
       </c>
-      <c r="AD2" s="72">
+      <c r="AD2" s="75">
         <v>337</v>
       </c>
-      <c r="AE2" s="74">
+      <c r="AE2" s="77">
         <v>339</v>
       </c>
-      <c r="AF2" s="76">
+      <c r="AF2" s="79">
         <v>190</v>
       </c>
-      <c r="AG2" s="78">
+      <c r="AG2" s="81">
         <v>69</v>
       </c>
     </row>
@@ -1658,91 +2013,91 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="25">
         <v>13123</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="27">
         <v>13040</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="29">
         <v>2711</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="31">
         <v>3250</v>
       </c>
-      <c r="I3" s="30">
+      <c r="I3" s="33">
         <v>3142</v>
       </c>
-      <c r="J3" s="32">
+      <c r="J3" s="35">
         <v>3532</v>
       </c>
-      <c r="K3" s="34">
+      <c r="K3" s="37">
         <v>3679</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="39">
         <v>3559</v>
       </c>
-      <c r="M3" s="38">
+      <c r="M3" s="41">
         <v>3501</v>
       </c>
-      <c r="N3" s="40">
+      <c r="N3" s="43">
         <v>1961</v>
       </c>
-      <c r="O3" s="42">
+      <c r="O3" s="45">
         <v>828</v>
       </c>
-      <c r="P3" s="44">
+      <c r="P3" s="47">
         <v>1313</v>
       </c>
-      <c r="Q3" s="46">
+      <c r="Q3" s="49">
         <v>1662</v>
       </c>
-      <c r="R3" s="48">
+      <c r="R3" s="51">
         <v>1647</v>
       </c>
-      <c r="S3" s="50">
+      <c r="S3" s="53">
         <v>1775</v>
       </c>
-      <c r="T3" s="52">
+      <c r="T3" s="55">
         <v>1894</v>
       </c>
-      <c r="U3" s="54">
+      <c r="U3" s="57">
         <v>1785</v>
       </c>
-      <c r="V3" s="56">
+      <c r="V3" s="59">
         <v>1751</v>
       </c>
-      <c r="W3" s="58">
+      <c r="W3" s="61">
         <v>917</v>
       </c>
-      <c r="X3" s="60">
+      <c r="X3" s="63">
         <v>379</v>
       </c>
-      <c r="Y3" s="62">
+      <c r="Y3" s="65">
         <v>1398</v>
       </c>
-      <c r="Z3" s="64">
+      <c r="Z3" s="67">
         <v>1588</v>
       </c>
-      <c r="AA3" s="66">
+      <c r="AA3" s="69">
         <v>1495</v>
       </c>
-      <c r="AB3" s="68">
+      <c r="AB3" s="71">
         <v>1757</v>
       </c>
-      <c r="AC3" s="70">
+      <c r="AC3" s="73">
         <v>1785</v>
       </c>
-      <c r="AD3" s="72">
+      <c r="AD3" s="75">
         <v>1774</v>
       </c>
-      <c r="AE3" s="74">
+      <c r="AE3" s="77">
         <v>1750</v>
       </c>
-      <c r="AF3" s="76">
+      <c r="AF3" s="79">
         <v>1044</v>
       </c>
-      <c r="AG3" s="78">
+      <c r="AG3" s="81">
         <v>449</v>
       </c>
     </row>
@@ -1765,91 +2120,91 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="25">
         <v>7238</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="27">
         <v>7338</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="29">
         <v>1558</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="31">
         <v>1785</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="33">
         <v>1754</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="35">
         <v>2003</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="37">
         <v>1983</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="39">
         <v>1881</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="41">
         <v>1956</v>
       </c>
-      <c r="N4" s="40">
+      <c r="N4" s="43">
         <v>1160</v>
       </c>
-      <c r="O4" s="42">
+      <c r="O4" s="45">
         <v>496</v>
       </c>
-      <c r="P4" s="44">
+      <c r="P4" s="47">
         <v>797</v>
       </c>
-      <c r="Q4" s="46">
+      <c r="Q4" s="49">
         <v>901</v>
       </c>
-      <c r="R4" s="48">
+      <c r="R4" s="51">
         <v>912</v>
       </c>
-      <c r="S4" s="50">
+      <c r="S4" s="53">
         <v>1048</v>
       </c>
-      <c r="T4" s="52">
+      <c r="T4" s="55">
         <v>993</v>
       </c>
-      <c r="U4" s="54">
+      <c r="U4" s="57">
         <v>933</v>
       </c>
-      <c r="V4" s="56">
+      <c r="V4" s="59">
         <v>915</v>
       </c>
-      <c r="W4" s="58">
+      <c r="W4" s="61">
         <v>532</v>
       </c>
-      <c r="X4" s="60">
+      <c r="X4" s="63">
         <v>207</v>
       </c>
-      <c r="Y4" s="62">
+      <c r="Y4" s="65">
         <v>761</v>
       </c>
-      <c r="Z4" s="64">
+      <c r="Z4" s="67">
         <v>884</v>
       </c>
-      <c r="AA4" s="66">
+      <c r="AA4" s="69">
         <v>842</v>
       </c>
-      <c r="AB4" s="68">
+      <c r="AB4" s="71">
         <v>955</v>
       </c>
-      <c r="AC4" s="70">
+      <c r="AC4" s="73">
         <v>990</v>
       </c>
-      <c r="AD4" s="72">
+      <c r="AD4" s="75">
         <v>948</v>
       </c>
-      <c r="AE4" s="74">
+      <c r="AE4" s="77">
         <v>1041</v>
       </c>
-      <c r="AF4" s="76">
+      <c r="AF4" s="79">
         <v>628</v>
       </c>
-      <c r="AG4" s="78">
+      <c r="AG4" s="81">
         <v>289</v>
       </c>
     </row>
@@ -1872,91 +2227,91 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="25">
         <v>4379</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="27">
         <v>4310</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="29">
         <v>1107</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="31">
         <v>1347</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="33">
         <v>1479</v>
       </c>
-      <c r="J5" s="32">
+      <c r="J5" s="35">
         <v>1436</v>
       </c>
-      <c r="K5" s="34">
+      <c r="K5" s="37">
         <v>1231</v>
       </c>
-      <c r="L5" s="36">
+      <c r="L5" s="39">
         <v>900</v>
       </c>
-      <c r="M5" s="38">
+      <c r="M5" s="41">
         <v>701</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="43">
         <v>357</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="45">
         <v>131</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="47">
         <v>572</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="49">
         <v>703</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="51">
         <v>752</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="53">
         <v>737</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="55">
         <v>600</v>
       </c>
-      <c r="U5" s="54">
+      <c r="U5" s="57">
         <v>438</v>
       </c>
-      <c r="V5" s="56">
+      <c r="V5" s="59">
         <v>352</v>
       </c>
-      <c r="W5" s="58">
+      <c r="W5" s="61">
         <v>167</v>
       </c>
-      <c r="X5" s="60">
+      <c r="X5" s="63">
         <v>58</v>
       </c>
-      <c r="Y5" s="62">
+      <c r="Y5" s="65">
         <v>535</v>
       </c>
-      <c r="Z5" s="64">
+      <c r="Z5" s="67">
         <v>644</v>
       </c>
-      <c r="AA5" s="66">
+      <c r="AA5" s="69">
         <v>727</v>
       </c>
-      <c r="AB5" s="68">
+      <c r="AB5" s="71">
         <v>699</v>
       </c>
-      <c r="AC5" s="70">
+      <c r="AC5" s="73">
         <v>631</v>
       </c>
-      <c r="AD5" s="72">
+      <c r="AD5" s="75">
         <v>462</v>
       </c>
-      <c r="AE5" s="74">
+      <c r="AE5" s="77">
         <v>349</v>
       </c>
-      <c r="AF5" s="76">
+      <c r="AF5" s="79">
         <v>190</v>
       </c>
-      <c r="AG5" s="78">
+      <c r="AG5" s="81">
         <v>73</v>
       </c>
     </row>
@@ -1979,91 +2334,91 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="25">
         <v>3569</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="27">
         <v>3493</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="29">
         <v>837</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="31">
         <v>909</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="33">
         <v>781</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="35">
         <v>925</v>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="37">
         <v>965</v>
       </c>
-      <c r="L6" s="36">
+      <c r="L6" s="39">
         <v>887</v>
       </c>
-      <c r="M6" s="38">
+      <c r="M6" s="41">
         <v>973</v>
       </c>
-      <c r="N6" s="40">
+      <c r="N6" s="43">
         <v>588</v>
       </c>
-      <c r="O6" s="42">
+      <c r="O6" s="45">
         <v>197</v>
       </c>
-      <c r="P6" s="44">
+      <c r="P6" s="47">
         <v>400</v>
       </c>
-      <c r="Q6" s="46">
+      <c r="Q6" s="49">
         <v>470</v>
       </c>
-      <c r="R6" s="48">
+      <c r="R6" s="51">
         <v>410</v>
       </c>
-      <c r="S6" s="50">
+      <c r="S6" s="53">
         <v>473</v>
       </c>
-      <c r="T6" s="52">
+      <c r="T6" s="55">
         <v>477</v>
       </c>
-      <c r="U6" s="54">
+      <c r="U6" s="57">
         <v>446</v>
       </c>
-      <c r="V6" s="56">
+      <c r="V6" s="59">
         <v>501</v>
       </c>
-      <c r="W6" s="58">
+      <c r="W6" s="61">
         <v>293</v>
       </c>
-      <c r="X6" s="60">
+      <c r="X6" s="63">
         <v>99</v>
       </c>
-      <c r="Y6" s="62">
+      <c r="Y6" s="65">
         <v>437</v>
       </c>
-      <c r="Z6" s="64">
+      <c r="Z6" s="67">
         <v>439</v>
       </c>
-      <c r="AA6" s="66">
+      <c r="AA6" s="69">
         <v>371</v>
       </c>
-      <c r="AB6" s="68">
+      <c r="AB6" s="71">
         <v>452</v>
       </c>
-      <c r="AC6" s="70">
+      <c r="AC6" s="73">
         <v>488</v>
       </c>
-      <c r="AD6" s="72">
+      <c r="AD6" s="75">
         <v>441</v>
       </c>
-      <c r="AE6" s="74">
+      <c r="AE6" s="77">
         <v>472</v>
       </c>
-      <c r="AF6" s="76">
+      <c r="AF6" s="79">
         <v>295</v>
       </c>
-      <c r="AG6" s="78">
+      <c r="AG6" s="81">
         <v>98</v>
       </c>
     </row>
@@ -2086,91 +2441,91 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="25">
         <v>4621</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="27">
         <v>4659</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="29">
         <v>1254</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="31">
         <v>1385</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="33">
         <v>1156</v>
       </c>
-      <c r="J7" s="32">
+      <c r="J7" s="35">
         <v>1227</v>
       </c>
-      <c r="K7" s="34">
+      <c r="K7" s="37">
         <v>1182</v>
       </c>
-      <c r="L7" s="36">
+      <c r="L7" s="39">
         <v>1102</v>
       </c>
-      <c r="M7" s="38">
+      <c r="M7" s="41">
         <v>1107</v>
       </c>
-      <c r="N7" s="40">
+      <c r="N7" s="43">
         <v>608</v>
       </c>
-      <c r="O7" s="42">
+      <c r="O7" s="45">
         <v>259</v>
       </c>
-      <c r="P7" s="44">
+      <c r="P7" s="47">
         <v>627</v>
       </c>
-      <c r="Q7" s="46">
+      <c r="Q7" s="49">
         <v>706</v>
       </c>
-      <c r="R7" s="48">
+      <c r="R7" s="51">
         <v>594</v>
       </c>
-      <c r="S7" s="50">
+      <c r="S7" s="53">
         <v>603</v>
       </c>
-      <c r="T7" s="52">
+      <c r="T7" s="55">
         <v>572</v>
       </c>
-      <c r="U7" s="54">
+      <c r="U7" s="57">
         <v>543</v>
       </c>
-      <c r="V7" s="56">
+      <c r="V7" s="59">
         <v>566</v>
       </c>
-      <c r="W7" s="58">
+      <c r="W7" s="61">
         <v>297</v>
       </c>
-      <c r="X7" s="60">
+      <c r="X7" s="63">
         <v>113</v>
       </c>
-      <c r="Y7" s="62">
+      <c r="Y7" s="65">
         <v>627</v>
       </c>
-      <c r="Z7" s="64">
+      <c r="Z7" s="67">
         <v>679</v>
       </c>
-      <c r="AA7" s="66">
+      <c r="AA7" s="69">
         <v>562</v>
       </c>
-      <c r="AB7" s="68">
+      <c r="AB7" s="71">
         <v>624</v>
       </c>
-      <c r="AC7" s="70">
+      <c r="AC7" s="73">
         <v>610</v>
       </c>
-      <c r="AD7" s="72">
+      <c r="AD7" s="75">
         <v>559</v>
       </c>
-      <c r="AE7" s="74">
+      <c r="AE7" s="77">
         <v>541</v>
       </c>
-      <c r="AF7" s="76">
+      <c r="AF7" s="79">
         <v>311</v>
       </c>
-      <c r="AG7" s="78">
+      <c r="AG7" s="81">
         <v>146</v>
       </c>
     </row>
@@ -2193,91 +2548,91 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="25">
         <v>13891</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="27">
         <v>14160</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="29">
         <v>2961</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="31">
         <v>3647</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="33">
         <v>3514</v>
       </c>
-      <c r="J8" s="32">
+      <c r="J8" s="35">
         <v>3796</v>
       </c>
-      <c r="K8" s="34">
+      <c r="K8" s="37">
         <v>3706</v>
       </c>
-      <c r="L8" s="36">
+      <c r="L8" s="39">
         <v>3554</v>
       </c>
-      <c r="M8" s="38">
+      <c r="M8" s="41">
         <v>3798</v>
       </c>
-      <c r="N8" s="40">
+      <c r="N8" s="43">
         <v>2173</v>
       </c>
-      <c r="O8" s="42">
+      <c r="O8" s="45">
         <v>902</v>
       </c>
-      <c r="P8" s="44">
+      <c r="P8" s="47">
         <v>1538</v>
       </c>
-      <c r="Q8" s="46">
+      <c r="Q8" s="49">
         <v>1922</v>
       </c>
-      <c r="R8" s="48">
+      <c r="R8" s="51">
         <v>1824</v>
       </c>
-      <c r="S8" s="50">
+      <c r="S8" s="53">
         <v>1828</v>
       </c>
-      <c r="T8" s="52">
+      <c r="T8" s="55">
         <v>1868</v>
       </c>
-      <c r="U8" s="54">
+      <c r="U8" s="57">
         <v>1679</v>
       </c>
-      <c r="V8" s="56">
+      <c r="V8" s="59">
         <v>1785</v>
       </c>
-      <c r="W8" s="58">
+      <c r="W8" s="61">
         <v>1040</v>
       </c>
-      <c r="X8" s="60">
+      <c r="X8" s="63">
         <v>407</v>
       </c>
-      <c r="Y8" s="62">
+      <c r="Y8" s="65">
         <v>1423</v>
       </c>
-      <c r="Z8" s="64">
+      <c r="Z8" s="67">
         <v>1725</v>
       </c>
-      <c r="AA8" s="66">
+      <c r="AA8" s="69">
         <v>1690</v>
       </c>
-      <c r="AB8" s="68">
+      <c r="AB8" s="71">
         <v>1968</v>
       </c>
-      <c r="AC8" s="70">
+      <c r="AC8" s="73">
         <v>1838</v>
       </c>
-      <c r="AD8" s="72">
+      <c r="AD8" s="75">
         <v>1875</v>
       </c>
-      <c r="AE8" s="74">
+      <c r="AE8" s="77">
         <v>2013</v>
       </c>
-      <c r="AF8" s="76">
+      <c r="AF8" s="79">
         <v>1133</v>
       </c>
-      <c r="AG8" s="78">
+      <c r="AG8" s="81">
         <v>495</v>
       </c>
     </row>
@@ -2300,91 +2655,91 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="25">
         <v>8696</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="27">
         <v>8574</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="29">
         <v>1826</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="31">
         <v>2255</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="33">
         <v>1986</v>
       </c>
-      <c r="J9" s="32">
+      <c r="J9" s="35">
         <v>2304</v>
       </c>
-      <c r="K9" s="34">
+      <c r="K9" s="37">
         <v>2548</v>
       </c>
-      <c r="L9" s="36">
+      <c r="L9" s="39">
         <v>2172</v>
       </c>
-      <c r="M9" s="38">
+      <c r="M9" s="41">
         <v>2200</v>
       </c>
-      <c r="N9" s="40">
+      <c r="N9" s="43">
         <v>1391</v>
       </c>
-      <c r="O9" s="42">
+      <c r="O9" s="45">
         <v>588</v>
       </c>
-      <c r="P9" s="44">
+      <c r="P9" s="47">
         <v>948</v>
       </c>
-      <c r="Q9" s="46">
+      <c r="Q9" s="49">
         <v>1149</v>
       </c>
-      <c r="R9" s="48">
+      <c r="R9" s="51">
         <v>1034</v>
       </c>
-      <c r="S9" s="50">
+      <c r="S9" s="53">
         <v>1181</v>
       </c>
-      <c r="T9" s="52">
+      <c r="T9" s="55">
         <v>1306</v>
       </c>
-      <c r="U9" s="54">
+      <c r="U9" s="57">
         <v>1108</v>
       </c>
-      <c r="V9" s="56">
+      <c r="V9" s="59">
         <v>1075</v>
       </c>
-      <c r="W9" s="58">
+      <c r="W9" s="61">
         <v>630</v>
       </c>
-      <c r="X9" s="60">
+      <c r="X9" s="63">
         <v>265</v>
       </c>
-      <c r="Y9" s="62">
+      <c r="Y9" s="65">
         <v>878</v>
       </c>
-      <c r="Z9" s="64">
+      <c r="Z9" s="67">
         <v>1106</v>
       </c>
-      <c r="AA9" s="66">
+      <c r="AA9" s="69">
         <v>952</v>
       </c>
-      <c r="AB9" s="68">
+      <c r="AB9" s="71">
         <v>1123</v>
       </c>
-      <c r="AC9" s="70">
+      <c r="AC9" s="73">
         <v>1242</v>
       </c>
-      <c r="AD9" s="72">
+      <c r="AD9" s="75">
         <v>1064</v>
       </c>
-      <c r="AE9" s="74">
+      <c r="AE9" s="77">
         <v>1125</v>
       </c>
-      <c r="AF9" s="76">
+      <c r="AF9" s="79">
         <v>761</v>
       </c>
-      <c r="AG9" s="78">
+      <c r="AG9" s="81">
         <v>323</v>
       </c>
     </row>
@@ -2407,91 +2762,91 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="25">
         <v>3264</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="27">
         <v>3329</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="29">
         <v>816</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="31">
         <v>982</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="33">
         <v>955</v>
       </c>
-      <c r="J10" s="32">
+      <c r="J10" s="35">
         <v>950</v>
       </c>
-      <c r="K10" s="34">
+      <c r="K10" s="37">
         <v>942</v>
       </c>
-      <c r="L10" s="36">
+      <c r="L10" s="39">
         <v>710</v>
       </c>
-      <c r="M10" s="38">
+      <c r="M10" s="41">
         <v>662</v>
       </c>
-      <c r="N10" s="40">
+      <c r="N10" s="43">
         <v>405</v>
       </c>
-      <c r="O10" s="42">
+      <c r="O10" s="45">
         <v>171</v>
       </c>
-      <c r="P10" s="44">
+      <c r="P10" s="47">
         <v>396</v>
       </c>
-      <c r="Q10" s="46">
+      <c r="Q10" s="49">
         <v>507</v>
       </c>
-      <c r="R10" s="48">
+      <c r="R10" s="51">
         <v>457</v>
       </c>
-      <c r="S10" s="50">
+      <c r="S10" s="53">
         <v>479</v>
       </c>
-      <c r="T10" s="52">
+      <c r="T10" s="55">
         <v>493</v>
       </c>
-      <c r="U10" s="54">
+      <c r="U10" s="57">
         <v>346</v>
       </c>
-      <c r="V10" s="56">
+      <c r="V10" s="59">
         <v>296</v>
       </c>
-      <c r="W10" s="58">
+      <c r="W10" s="61">
         <v>200</v>
       </c>
-      <c r="X10" s="60">
+      <c r="X10" s="63">
         <v>90</v>
       </c>
-      <c r="Y10" s="62">
+      <c r="Y10" s="65">
         <v>420</v>
       </c>
-      <c r="Z10" s="64">
+      <c r="Z10" s="67">
         <v>475</v>
       </c>
-      <c r="AA10" s="66">
+      <c r="AA10" s="69">
         <v>498</v>
       </c>
-      <c r="AB10" s="68">
+      <c r="AB10" s="71">
         <v>471</v>
       </c>
-      <c r="AC10" s="70">
+      <c r="AC10" s="73">
         <v>449</v>
       </c>
-      <c r="AD10" s="72">
+      <c r="AD10" s="75">
         <v>364</v>
       </c>
-      <c r="AE10" s="74">
+      <c r="AE10" s="77">
         <v>366</v>
       </c>
-      <c r="AF10" s="76">
+      <c r="AF10" s="79">
         <v>205</v>
       </c>
-      <c r="AG10" s="78">
+      <c r="AG10" s="81">
         <v>81</v>
       </c>
     </row>
@@ -2514,91 +2869,91 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="25">
         <v>3528</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="27">
         <v>3438</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="29">
         <v>816</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="31">
         <v>851</v>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="33">
         <v>854</v>
       </c>
-      <c r="J11" s="32">
+      <c r="J11" s="35">
         <v>941</v>
       </c>
-      <c r="K11" s="34">
+      <c r="K11" s="37">
         <v>970</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="39">
         <v>946</v>
       </c>
-      <c r="M11" s="38">
+      <c r="M11" s="41">
         <v>866</v>
       </c>
-      <c r="N11" s="40">
+      <c r="N11" s="43">
         <v>502</v>
       </c>
-      <c r="O11" s="42">
+      <c r="O11" s="45">
         <v>220</v>
       </c>
-      <c r="P11" s="44">
+      <c r="P11" s="47">
         <v>444</v>
       </c>
-      <c r="Q11" s="46">
+      <c r="Q11" s="49">
         <v>444</v>
       </c>
-      <c r="R11" s="48">
+      <c r="R11" s="51">
         <v>424</v>
       </c>
-      <c r="S11" s="50">
+      <c r="S11" s="53">
         <v>471</v>
       </c>
-      <c r="T11" s="52">
+      <c r="T11" s="55">
         <v>490</v>
       </c>
-      <c r="U11" s="54">
+      <c r="U11" s="57">
         <v>487</v>
       </c>
-      <c r="V11" s="56">
+      <c r="V11" s="59">
         <v>436</v>
       </c>
-      <c r="W11" s="58">
+      <c r="W11" s="61">
         <v>233</v>
       </c>
-      <c r="X11" s="60">
+      <c r="X11" s="63">
         <v>99</v>
       </c>
-      <c r="Y11" s="62">
+      <c r="Y11" s="65">
         <v>372</v>
       </c>
-      <c r="Z11" s="64">
+      <c r="Z11" s="67">
         <v>407</v>
       </c>
-      <c r="AA11" s="66">
+      <c r="AA11" s="69">
         <v>430</v>
       </c>
-      <c r="AB11" s="68">
+      <c r="AB11" s="71">
         <v>470</v>
       </c>
-      <c r="AC11" s="70">
+      <c r="AC11" s="73">
         <v>480</v>
       </c>
-      <c r="AD11" s="72">
+      <c r="AD11" s="75">
         <v>459</v>
       </c>
-      <c r="AE11" s="74">
+      <c r="AE11" s="77">
         <v>430</v>
       </c>
-      <c r="AF11" s="76">
+      <c r="AF11" s="79">
         <v>269</v>
       </c>
-      <c r="AG11" s="78">
+      <c r="AG11" s="81">
         <v>121</v>
       </c>
     </row>
@@ -2621,200 +2976,200 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="25">
         <v>5983</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="27">
         <v>6424</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="29">
         <v>1133</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="31">
         <v>1569</v>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="33">
         <v>1519</v>
       </c>
-      <c r="J12" s="32">
+      <c r="J12" s="35">
         <v>1695</v>
       </c>
-      <c r="K12" s="34">
+      <c r="K12" s="37">
         <v>1875</v>
       </c>
-      <c r="L12" s="36">
+      <c r="L12" s="39">
         <v>1727</v>
       </c>
-      <c r="M12" s="38">
+      <c r="M12" s="41">
         <v>1627</v>
       </c>
-      <c r="N12" s="40">
+      <c r="N12" s="43">
         <v>885</v>
       </c>
-      <c r="O12" s="42">
+      <c r="O12" s="45">
         <v>377</v>
       </c>
-      <c r="P12" s="44">
+      <c r="P12" s="47">
         <v>586</v>
       </c>
-      <c r="Q12" s="46">
+      <c r="Q12" s="49">
         <v>785</v>
       </c>
-      <c r="R12" s="48">
+      <c r="R12" s="51">
         <v>773</v>
       </c>
-      <c r="S12" s="50">
+      <c r="S12" s="53">
         <v>800</v>
       </c>
-      <c r="T12" s="52">
+      <c r="T12" s="55">
         <v>874</v>
       </c>
-      <c r="U12" s="54">
+      <c r="U12" s="57">
         <v>826</v>
       </c>
-      <c r="V12" s="56">
+      <c r="V12" s="59">
         <v>781</v>
       </c>
-      <c r="W12" s="58">
+      <c r="W12" s="61">
         <v>388</v>
       </c>
-      <c r="X12" s="60">
+      <c r="X12" s="63">
         <v>170</v>
       </c>
-      <c r="Y12" s="62">
+      <c r="Y12" s="65">
         <v>547</v>
       </c>
-      <c r="Z12" s="64">
+      <c r="Z12" s="67">
         <v>784</v>
       </c>
-      <c r="AA12" s="66">
+      <c r="AA12" s="69">
         <v>746</v>
       </c>
-      <c r="AB12" s="68">
+      <c r="AB12" s="71">
         <v>895</v>
       </c>
-      <c r="AC12" s="70">
+      <c r="AC12" s="73">
         <v>1001</v>
       </c>
-      <c r="AD12" s="72">
+      <c r="AD12" s="75">
         <v>901</v>
       </c>
-      <c r="AE12" s="74">
+      <c r="AE12" s="77">
         <v>846</v>
       </c>
-      <c r="AF12" s="76">
+      <c r="AF12" s="79">
         <v>497</v>
       </c>
-      <c r="AG12" s="78">
+      <c r="AG12" s="81">
         <v>207</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="26">
         <v>70775</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="28">
         <v>71255</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="30">
         <v>15565</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="32">
         <v>18600</v>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="34">
         <v>17707</v>
       </c>
-      <c r="J13" s="33">
+      <c r="J13" s="36">
         <v>19522</v>
       </c>
-      <c r="K13" s="35">
+      <c r="K13" s="38">
         <v>19785</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="40">
         <v>18084</v>
       </c>
-      <c r="M13" s="39">
+      <c r="M13" s="42">
         <v>18077</v>
       </c>
-      <c r="N13" s="41">
+      <c r="N13" s="44">
         <v>10393</v>
       </c>
-      <c r="O13" s="43">
+      <c r="O13" s="46">
         <v>4297</v>
       </c>
-      <c r="P13" s="45">
+      <c r="P13" s="48">
         <v>7900</v>
       </c>
-      <c r="Q13" s="47">
+      <c r="Q13" s="50">
         <v>9573</v>
       </c>
-      <c r="R13" s="49">
+      <c r="R13" s="52">
         <v>9107</v>
       </c>
-      <c r="S13" s="51">
+      <c r="S13" s="54">
         <v>9749</v>
       </c>
-      <c r="T13" s="53">
+      <c r="T13" s="56">
         <v>9925</v>
       </c>
-      <c r="U13" s="55">
+      <c r="U13" s="58">
         <v>8900</v>
       </c>
-      <c r="V13" s="57">
+      <c r="V13" s="60">
         <v>8805</v>
       </c>
-      <c r="W13" s="59">
+      <c r="W13" s="62">
         <v>4870</v>
       </c>
-      <c r="X13" s="61">
+      <c r="X13" s="64">
         <v>1946</v>
       </c>
-      <c r="Y13" s="63">
+      <c r="Y13" s="66">
         <v>7665</v>
       </c>
-      <c r="Z13" s="65">
+      <c r="Z13" s="68">
         <v>9027</v>
       </c>
-      <c r="AA13" s="67">
+      <c r="AA13" s="70">
         <v>8600</v>
       </c>
-      <c r="AB13" s="69">
+      <c r="AB13" s="72">
         <v>9773</v>
       </c>
-      <c r="AC13" s="71">
+      <c r="AC13" s="74">
         <v>9860</v>
       </c>
-      <c r="AD13" s="73">
+      <c r="AD13" s="76">
         <v>9184</v>
       </c>
-      <c r="AE13" s="75">
+      <c r="AE13" s="78">
         <v>9272</v>
       </c>
-      <c r="AF13" s="77">
+      <c r="AF13" s="80">
         <v>5523</v>
       </c>
-      <c r="AG13" s="79">
+      <c r="AG13" s="82">
         <v>2351</v>
       </c>
     </row>
@@ -2830,46 +3185,46 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="59.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="60.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="84" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="84" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="84" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="84" t="inlineStr">
         <is>
           <t>Tasa de Natalidad</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="84" t="inlineStr">
         <is>
           <t>Tasa de Mortalidad</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="84" t="inlineStr">
         <is>
           <t>Índice de Envejecimiento</t>
         </is>
@@ -2894,14 +3249,14 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E2" s="80">
+      <c r="E2" s="86">
         <v>6.75381263616558</v>
       </c>
-      <c r="F2" s="82">
+      <c r="F2" s="88">
         <v>9.657594381036</v>
       </c>
-      <c r="G2" s="84">
-        <v>39.6763119176067</v>
+      <c r="G2" s="90">
+        <v>37.2231216430664</v>
       </c>
     </row>
     <row r="3">
@@ -2923,14 +3278,14 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E3" s="80">
+      <c r="E3" s="86">
         <v>4.08367685017529</v>
       </c>
-      <c r="F3" s="82">
+      <c r="F3" s="88">
         <v>5.79157934844732</v>
       </c>
-      <c r="G3" s="84">
-        <v>41.0769664505216</v>
+      <c r="G3" s="90">
+        <v>39.251636505127</v>
       </c>
     </row>
     <row r="4">
@@ -2952,14 +3307,14 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E4" s="80">
+      <c r="E4" s="86">
         <v>5.13542033063665</v>
       </c>
-      <c r="F4" s="82">
+      <c r="F4" s="88">
         <v>6.705315359363</v>
       </c>
-      <c r="G4" s="84">
-        <v>42.4242424242424</v>
+      <c r="G4" s="90">
+        <v>40.0336418151855</v>
       </c>
     </row>
     <row r="5">
@@ -2981,14 +3336,14 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E5" s="80">
+      <c r="E5" s="86">
         <v>8.68544600938967</v>
       </c>
-      <c r="F5" s="82">
+      <c r="F5" s="88">
         <v>6.66354921674071</v>
       </c>
-      <c r="G5" s="84">
-        <v>26.8671848597499</v>
+      <c r="G5" s="90">
+        <v>25.8411846160889</v>
       </c>
     </row>
     <row r="6">
@@ -3010,14 +3365,14 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="86">
         <v>5.75060532687651</v>
       </c>
-      <c r="F6" s="82">
+      <c r="F6" s="88">
         <v>10.0075815011372</v>
       </c>
-      <c r="G6" s="84">
-        <v>40.8276311502118</v>
+      <c r="G6" s="90">
+        <v>38.0446319580078</v>
       </c>
     </row>
     <row r="7">
@@ -3039,14 +3394,14 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E7" s="80">
+      <c r="E7" s="86">
         <v>6.23399755092953</v>
       </c>
-      <c r="F7" s="82">
+      <c r="F7" s="88">
         <v>6.19469026548673</v>
       </c>
-      <c r="G7" s="84">
-        <v>34.9556400506971</v>
+      <c r="G7" s="90">
+        <v>32.1866035461426</v>
       </c>
     </row>
     <row r="8">
@@ -3068,14 +3423,14 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E8" s="80">
+      <c r="E8" s="86">
         <v>4.19716257934718</v>
       </c>
-      <c r="F8" s="82">
+      <c r="F8" s="88">
         <v>6.82184361180625</v>
       </c>
-      <c r="G8" s="84">
-        <v>41.4425218434127</v>
+      <c r="G8" s="90">
+        <v>39.0538864135742</v>
       </c>
     </row>
     <row r="9">
@@ -3097,14 +3452,14 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E9" s="80">
+      <c r="E9" s="86">
         <v>5.22930816854</v>
       </c>
-      <c r="F9" s="82">
+      <c r="F9" s="88">
         <v>6.11657471815783</v>
       </c>
-      <c r="G9" s="84">
-        <v>42.1207041072925</v>
+      <c r="G9" s="90">
+        <v>39.4844169616699</v>
       </c>
     </row>
     <row r="10">
@@ -3126,14 +3481,14 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E10" s="80">
+      <c r="E10" s="86">
         <v>5.25502318392581</v>
       </c>
-      <c r="F10" s="82">
+      <c r="F10" s="88">
         <v>7.50382848392037</v>
       </c>
-      <c r="G10" s="84">
-        <v>35.0925561244584</v>
+      <c r="G10" s="90">
+        <v>32.3949241638184</v>
       </c>
     </row>
     <row r="11">
@@ -3155,14 +3510,14 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E11" s="80">
+      <c r="E11" s="86">
         <v>4.04979751012449</v>
       </c>
-      <c r="F11" s="82">
+      <c r="F11" s="88">
         <v>4.78826874158312</v>
       </c>
-      <c r="G11" s="84">
-        <v>39.1687213807679</v>
+      <c r="G11" s="90">
+        <v>40.0881042480469</v>
       </c>
     </row>
     <row r="12">
@@ -3184,107 +3539,107 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E12" s="80">
+      <c r="E12" s="86">
         <v>7.20013091147112</v>
       </c>
-      <c r="F12" s="82">
+      <c r="F12" s="88">
         <v>7.61565259661347</v>
       </c>
-      <c r="G12" s="84">
-        <v>41.9213973799127</v>
+      <c r="G12" s="90">
+        <v>39.0305595397949</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA CARTAMA (por población)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E13" s="81">
+      <c r="E13" s="87">
         <v>5.25739639632487</v>
       </c>
-      <c r="F13" s="83">
+      <c r="F13" s="89">
         <v>6.72686073878917</v>
       </c>
-      <c r="G13" s="85">
-        <v>39.8011024208227</v>
+      <c r="G13" s="91">
+        <v>37.6257353354912</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN SUROESTE (por población)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E14" s="81">
+      <c r="E14" s="87">
         <v>6.92904727483559</v>
       </c>
-      <c r="F14" s="83">
+      <c r="F14" s="89">
         <v>6.40577371612409</v>
       </c>
-      <c r="G14" s="85">
-        <v>35.2555158114219</v>
+      <c r="G14" s="91">
+        <v>33.1374676591258</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E15" s="81">
+      <c r="E15" s="87">
         <v>8.63819084562528</v>
       </c>
-      <c r="F15" s="83">
+      <c r="F15" s="89">
         <v>5.63888092494404</v>
       </c>
-      <c r="G15" s="85">
-        <v>32.052654940463</v>
+      <c r="G15" s="91">
+        <v>31.7311728877886</v>
       </c>
     </row>
   </sheetData>
@@ -3299,47 +3654,47 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="59.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="60.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="93" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="93" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="93" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - cabecera municipal</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - centros poblados y rural</t>
         </is>
@@ -3364,13 +3719,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E2" s="86">
+      <c r="E2" s="95">
         <v>1.16311003716751</v>
       </c>
-      <c r="F2" s="88">
+      <c r="F2" s="97">
         <v>1.80236463791482</v>
       </c>
-      <c r="G2" s="90">
+      <c r="G2" s="99">
         <v>0.509362854787424</v>
       </c>
     </row>
@@ -3393,13 +3748,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E3" s="86">
+      <c r="E3" s="95">
         <v>0.356440511307768</v>
       </c>
-      <c r="F3" s="88">
+      <c r="F3" s="97">
         <v>0</v>
       </c>
-      <c r="G3" s="90">
+      <c r="G3" s="99">
         <v>0.568944509840365</v>
       </c>
     </row>
@@ -3422,13 +3777,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E4" s="86">
+      <c r="E4" s="95">
         <v>0</v>
       </c>
-      <c r="F4" s="88">
+      <c r="F4" s="97">
         <v>0</v>
       </c>
-      <c r="G4" s="90">
+      <c r="G4" s="99">
         <v>0</v>
       </c>
     </row>
@@ -3451,13 +3806,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E5" s="86">
+      <c r="E5" s="95">
         <v>1.06538660266347</v>
       </c>
-      <c r="F5" s="88">
+      <c r="F5" s="97">
         <v>1.10727962283403</v>
       </c>
-      <c r="G5" s="90">
+      <c r="G5" s="99">
         <v>0.671521035598706</v>
       </c>
     </row>
@@ -3480,13 +3835,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E6" s="86">
+      <c r="E6" s="95">
         <v>0</v>
       </c>
-      <c r="F6" s="88">
+      <c r="F6" s="97">
         <v>0</v>
       </c>
-      <c r="G6" s="90">
+      <c r="G6" s="99">
         <v>0</v>
       </c>
     </row>
@@ -3509,13 +3864,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="95">
         <v>0.600065760631302</v>
       </c>
-      <c r="F7" s="88">
+      <c r="F7" s="97">
         <v>0.751806287834408</v>
       </c>
-      <c r="G7" s="90">
+      <c r="G7" s="99">
         <v>0.405945540844366</v>
       </c>
     </row>
@@ -3538,13 +3893,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E8" s="86">
+      <c r="E8" s="95">
         <v>0.308050300816243</v>
       </c>
-      <c r="F8" s="88">
+      <c r="F8" s="97">
         <v>0.613504298131874</v>
       </c>
-      <c r="G8" s="90">
+      <c r="G8" s="99">
         <v>0</v>
       </c>
     </row>
@@ -3567,13 +3922,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E9" s="86">
+      <c r="E9" s="95">
         <v>0</v>
       </c>
-      <c r="F9" s="88">
+      <c r="F9" s="97">
         <v>0</v>
       </c>
-      <c r="G9" s="90">
+      <c r="G9" s="99">
         <v>0</v>
       </c>
     </row>
@@ -3596,13 +3951,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E10" s="86">
+      <c r="E10" s="95">
         <v>0.630239192451174</v>
       </c>
-      <c r="F10" s="88">
+      <c r="F10" s="97">
         <v>1.07236203420208</v>
       </c>
-      <c r="G10" s="90">
+      <c r="G10" s="99">
         <v>0</v>
       </c>
     </row>
@@ -3625,13 +3980,13 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E11" s="86">
+      <c r="E11" s="95">
         <v>0.856845064960248</v>
       </c>
-      <c r="F11" s="88">
+      <c r="F11" s="97">
         <v>0.302162849872775</v>
       </c>
-      <c r="G11" s="90">
+      <c r="G11" s="99">
         <v>1.72317436661699</v>
       </c>
     </row>
@@ -3654,106 +4009,106 @@
           <t>PROVINCIA CARTAMA</t>
         </is>
       </c>
-      <c r="E12" s="86">
+      <c r="E12" s="95">
         <v>0.147444298820445</v>
       </c>
-      <c r="F12" s="88">
+      <c r="F12" s="97">
         <v>0.301861479121247</v>
       </c>
-      <c r="G12" s="90">
+      <c r="G12" s="99">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA CARTAMA (por población)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E13" s="87">
+      <c r="E13" s="96">
         <v>0.3543654686733</v>
       </c>
-      <c r="F13" s="89">
+      <c r="F13" s="98">
         <v>0.391823964433792</v>
       </c>
-      <c r="G13" s="91">
+      <c r="G13" s="100">
         <v>0.271446073908791</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN SUROESTE (por población)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E14" s="87">
+      <c r="E14" s="96">
         <v>1.25549527009051</v>
       </c>
-      <c r="F14" s="89">
+      <c r="F14" s="98">
         <v>1.07680558118976</v>
       </c>
-      <c r="G14" s="91">
+      <c r="G14" s="100">
         <v>1.36215462092775</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E15" s="87">
+      <c r="E15" s="96">
         <v>2.43784156596946</v>
       </c>
-      <c r="F15" s="89">
+      <c r="F15" s="98">
         <v>2.2991539975123</v>
       </c>
-      <c r="G15" s="91">
+      <c r="G15" s="100">
         <v>2.88568680338064</v>
       </c>
     </row>
@@ -3769,23 +4124,23 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="102" t="inlineStr">
         <is>
           <t>habitantes_total</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="102" t="inlineStr">
         <is>
           <t>part_total_prov</t>
         </is>
@@ -3946,35 +4301,35 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="104" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="104" t="inlineStr">
         <is>
           <t>habitantes_cabecera</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="104" t="inlineStr">
         <is>
           <t>pct_cabecera</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="104" t="inlineStr">
         <is>
           <t>habitantes_rural</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="104" t="inlineStr">
         <is>
           <t>pct_rural</t>
         </is>
@@ -4201,22 +4556,23 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="106" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="106" t="inlineStr">
         <is>
           <t>habitantes_total</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="106" t="inlineStr">
         <is>
           <t>densidad_pob</t>
         </is>
@@ -4377,23 +4733,23 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="108" t="inlineStr">
         <is>
           <t>banda</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="108" t="inlineStr">
         <is>
           <t>sexo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="108" t="inlineStr">
         <is>
           <t>personas</t>
         </is>
@@ -4681,17 +5037,17 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="110" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="110" t="inlineStr">
         <is>
           <t>I_enve_T</t>
         </is>
@@ -4704,7 +5060,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>39.6763119176067</v>
+        <v>37.2231216430664</v>
       </c>
     </row>
     <row r="3">
@@ -4714,7 +5070,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>41.0769664505216</v>
+        <v>39.251636505127</v>
       </c>
     </row>
     <row r="4">
@@ -4724,7 +5080,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>42.4242424242424</v>
+        <v>40.0336418151855</v>
       </c>
     </row>
     <row r="5">
@@ -4734,7 +5090,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>26.8671848597499</v>
+        <v>25.8411846160889</v>
       </c>
     </row>
     <row r="6">
@@ -4744,7 +5100,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>40.8276311502118</v>
+        <v>38.0446319580078</v>
       </c>
     </row>
     <row r="7">
@@ -4754,7 +5110,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>34.9556400506971</v>
+        <v>32.1866035461426</v>
       </c>
     </row>
     <row r="8">
@@ -4764,7 +5120,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>41.4425218434127</v>
+        <v>39.0538864135742</v>
       </c>
     </row>
     <row r="9">
@@ -4774,7 +5130,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>42.1207041072925</v>
+        <v>39.4844169616699</v>
       </c>
     </row>
     <row r="10">
@@ -4784,7 +5140,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>35.0925561244584</v>
+        <v>32.3949241638184</v>
       </c>
     </row>
     <row r="11">
@@ -4794,7 +5150,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>39.1687213807679</v>
+        <v>40.0881042480469</v>
       </c>
     </row>
     <row r="12">
@@ -4804,7 +5160,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>41.9213973799127</v>
+        <v>39.0305595397949</v>
       </c>
     </row>
   </sheetData>
